--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,10 +260,10 @@
     <t>ADMINISTRATIVE COST BALANCE (-73)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.marshallFee</t>
-  </si>
-  <si>
-    <t>MARSHALL FEE (-74)</t>
+    <t>AccountsReceivable430.marshalFee</t>
+  </si>
+  <si>
+    <t>MARSHAL FEE (-74)</t>
   </si>
   <si>
     <t>AccountsReceivable430.courtCost</t>
@@ -290,10 +290,10 @@
     <t>TOTAL PAID ADMINISTRATIVE COST (-79)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.totalPaidMarshallFee</t>
-  </si>
-  <si>
-    <t>TOTAL PAID MARSHALL FEE (-79.1)</t>
+    <t>AccountsReceivable430.totalPaidMarshalFee</t>
+  </si>
+  <si>
+    <t>TOTAL PAID MARSHAL FEE (-79.1)</t>
   </si>
   <si>
     <t>AccountsReceivable430.totalPaidCourtCost</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>AccountsReceivable430.administrativeCostBalance</t>
+    <t>AccountsReceivable430.totalPaidMarshalFee</t>
   </si>
   <si>
     <t>1</t>
@@ -257,15 +257,21 @@
 </t>
   </si>
   <si>
+    <t>TOTAL PAID MARSHAL FEE (-79.1)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.marshalFee</t>
+  </si>
+  <si>
+    <t>MARSHAL FEE (-74)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.administrativeCostBalance</t>
+  </si>
+  <si>
     <t>ADMINISTRATIVE COST BALANCE (-73)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.marshalFee</t>
-  </si>
-  <si>
-    <t>MARSHAL FEE (-74)</t>
-  </si>
-  <si>
     <t>AccountsReceivable430.courtCost</t>
   </si>
   <si>
@@ -288,12 +294,6 @@
   </si>
   <si>
     <t>TOTAL PAID ADMINISTRATIVE COST (-79)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.totalPaidMarshalFee</t>
-  </si>
-  <si>
-    <t>TOTAL PAID MARSHAL FEE (-79.1)</t>
   </si>
   <si>
     <t>AccountsReceivable430.totalPaidCourtCost</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file ACCOUNTS RECEIVABLE (430)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source ACCOUNTS RECEIVABLE (430)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="98">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>AccountsReceivable430.totalPaidMarshalFee</t>
+    <t>AccountsReceivable430.administrativeCostBalance</t>
   </si>
   <si>
     <t>1</t>
@@ -257,49 +257,59 @@
 </t>
   </si>
   <si>
+    <t>ADMINISTRATIVE COST BALANCE (-73)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.marshalFee</t>
+  </si>
+  <si>
+    <t>MARSHAL FEE (-74)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.courtCost</t>
+  </si>
+  <si>
+    <t>COURT COST (-75)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.totalPaidPrincipal</t>
+  </si>
+  <si>
+    <t>TOTAL PAID PRINCIPAL (-77)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.totalPaidInterest</t>
+  </si>
+  <si>
+    <t>TOTAL PAID INTEREST (-78)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.totalPaidAdministrativeCost</t>
+  </si>
+  <si>
+    <t>TOTAL PAID ADMINISTRATIVE COST (-79)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.totalPaidMarshalFee</t>
+  </si>
+  <si>
     <t>TOTAL PAID MARSHAL FEE (-79.1)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.marshalFee</t>
-  </si>
-  <si>
-    <t>MARSHAL FEE (-74)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.administrativeCostBalance</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIVE COST BALANCE (-73)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.courtCost</t>
-  </si>
-  <si>
-    <t>COURT COST (-75)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.totalPaidPrincipal</t>
-  </si>
-  <si>
-    <t>TOTAL PAID PRINCIPAL (-77)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.totalPaidInterest</t>
-  </si>
-  <si>
-    <t>TOTAL PAID INTEREST (-78)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.totalPaidAdministrativeCost</t>
-  </si>
-  <si>
-    <t>TOTAL PAID ADMINISTRATIVE COST (-79)</t>
-  </si>
-  <si>
     <t>AccountsReceivable430.totalPaidCourtCost</t>
   </si>
   <si>
     <t>TOTAL PAID COURT COST (-79.2)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.billNo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/IntegratedBillingAction350)
+</t>
+  </si>
+  <si>
+    <t>BILL NO. (-.01)</t>
   </si>
 </sst>
 </file>
@@ -601,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.12109375" customWidth="true" bestFit="true"/>
@@ -614,7 +624,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="8.95703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.47265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1651,6 +1661,106 @@
         <v>72</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="117">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,23 +247,91 @@
     <t>Base</t>
   </si>
   <si>
-    <t>AccountsReceivable430.administrativeCostBalance</t>
+    <t>AccountsReceivable430.debtor</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ArDebtor340)
+</t>
+  </si>
+  <si>
+    <t>DEBTOR (-9)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.name</t>
   </si>
   <si>
     <t xml:space="preserve">Element
 </t>
   </si>
   <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.currentStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/AccountsReceivableTranstype4303)
+</t>
+  </si>
+  <si>
+    <t>CURRENT STATUS (-8)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.patient</t>
+  </si>
+  <si>
+    <t>PATIENT (-7)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.dateBillPrepared</t>
+  </si>
+  <si>
+    <t>DATE BILL PREPARED (-10)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.originalAmount</t>
+  </si>
+  <si>
+    <t>ORIGINAL AMOUNT (-3)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.currentBalance</t>
+  </si>
+  <si>
+    <t>CURRENT BALANCE (-11)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.amendedAmount</t>
+  </si>
+  <si>
+    <t>AMENDED AMOUNT (-35)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.principalBalance</t>
+  </si>
+  <si>
+    <t>PRINCIPAL BALANCE (-71)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.interestBalance</t>
+  </si>
+  <si>
+    <t>INTEREST BALANCE (-72)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.administrativeCostBalance</t>
+  </si>
+  <si>
     <t>ADMINISTRATIVE COST BALANCE (-73)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.marshalFee</t>
-  </si>
-  <si>
-    <t>MARSHAL FEE (-74)</t>
+    <t>AccountsReceivable430.marshallFee</t>
+  </si>
+  <si>
+    <t>MARSHALL FEE (-74)</t>
   </si>
   <si>
     <t>AccountsReceivable430.courtCost</t>
@@ -300,16 +368,6 @@
   </si>
   <si>
     <t>TOTAL PAID COURT COST (-79.2)</t>
-  </si>
-  <si>
-    <t>AccountsReceivable430.billNo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/IntegratedBillingAction350)
-</t>
-  </si>
-  <si>
-    <t>BILL NO. (-.01)</t>
   </si>
 </sst>
 </file>
@@ -611,7 +669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.12109375" customWidth="true" bestFit="true"/>
@@ -624,7 +682,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.47265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -989,13 +1047,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1063,10 +1121,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1089,13 +1147,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1146,7 +1204,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1163,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1189,13 +1247,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1246,7 +1304,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1263,10 +1321,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1289,13 +1347,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1346,7 +1404,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1363,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1389,13 +1447,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1446,7 +1504,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1463,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1489,13 +1547,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1546,7 +1604,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1563,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1589,13 +1647,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1646,7 +1704,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1663,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1689,13 +1747,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1746,7 +1804,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1758,6 +1816,906 @@
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="119">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,20 @@
     <t>Base</t>
   </si>
   <si>
+    <t>AccountsReceivable430.patient</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element
+</t>
+  </si>
+  <si>
+    <t>PATIENT (-7)</t>
+  </si>
+  <si>
     <t>AccountsReceivable430.debtor</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ArDebtor340)
@@ -263,10 +273,6 @@
     <t>AccountsReceivable430.name</t>
   </si>
   <si>
-    <t xml:space="preserve">Element
-</t>
-  </si>
-  <si>
     <t>NAME (-.01)</t>
   </si>
   <si>
@@ -280,16 +286,16 @@
     <t>CURRENT STATUS (-8)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.patient</t>
-  </si>
-  <si>
-    <t>PATIENT (-7)</t>
-  </si>
-  <si>
     <t>AccountsReceivable430.dateBillPrepared</t>
   </si>
   <si>
     <t>DATE BILL PREPARED (-10)</t>
+  </si>
+  <si>
+    <t>AccountsReceivable430.site</t>
+  </si>
+  <si>
+    <t>SITE (-12)</t>
   </si>
   <si>
     <t>AccountsReceivable430.originalAmount</t>
@@ -669,7 +675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.12109375" customWidth="true" bestFit="true"/>
@@ -1147,13 +1153,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1221,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1247,7 +1253,7 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>88</v>
@@ -1304,7 +1310,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1347,7 +1353,7 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>90</v>
@@ -1447,7 +1453,7 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>92</v>
@@ -1547,7 +1553,7 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>94</v>
@@ -1647,7 +1653,7 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>96</v>
@@ -1747,7 +1753,7 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>98</v>
@@ -1847,7 +1853,7 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>100</v>
@@ -1947,7 +1953,7 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>102</v>
@@ -2047,7 +2053,7 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>104</v>
@@ -2147,7 +2153,7 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>106</v>
@@ -2247,7 +2253,7 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>108</v>
@@ -2347,7 +2353,7 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>110</v>
@@ -2447,7 +2453,7 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>112</v>
@@ -2547,7 +2553,7 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>114</v>
@@ -2647,7 +2653,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>116</v>
@@ -2716,6 +2722,106 @@
         <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,10 +270,10 @@
     <t>DEBTOR (-9)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.name</t>
-  </si>
-  <si>
-    <t>NAME (-.01)</t>
+    <t>AccountsReceivable430.billNo</t>
+  </si>
+  <si>
+    <t>BILL NO. (-.01)</t>
   </si>
   <si>
     <t>AccountsReceivable430.currentStatus</t>
@@ -334,10 +334,10 @@
     <t>ADMINISTRATIVE COST BALANCE (-73)</t>
   </si>
   <si>
-    <t>AccountsReceivable430.marshallFee</t>
-  </si>
-  <si>
-    <t>MARSHALL FEE (-74)</t>
+    <t>AccountsReceivable430.marshalFee</t>
+  </si>
+  <si>
+    <t>MARSHAL FEE (-74)</t>
   </si>
   <si>
     <t>AccountsReceivable430.courtCost</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AccountsReceivable430.xlsx
+++ b/docs/StructureDefinition-AccountsReceivable430.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
